--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90836</v>
+        <v>90839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>90847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90847</v>
+        <v>90848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90850</v>
+        <v>90856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90856</v>
+        <v>90948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21726-2025 artfynd.xlsx
+++ b/artfynd/A 21726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128038495</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>90960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
